--- a/Result/KEEL_Result/Ranking_KEEL.xlsx
+++ b/Result/KEEL_Result/Ranking_KEEL.xlsx
@@ -554,367 +554,397 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>EB-SMOTE</t>
+          <t>DualLexiBoost</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0.7968662926342671</v>
+        <v>0.782814826677541</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>0.6756423075740576</v>
+        <v>0.7176741264028473</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.9077386652419568</v>
+        <v>0.7930313422157159</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.7266522871957415</v>
+        <v>0.5361872527834445</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.6343188236772476</v>
+        <v>0.9753167352220332</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>FRAME</t>
+          <t>EB-SMOTE</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.8178774964065021</v>
+        <v>0.7968662926342671</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.7341250977373035</v>
+        <v>0.6756423075740576</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.8994935530326782</v>
+        <v>0.9077386652419568</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.7333340883925064</v>
+        <v>0.7266522871957415</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>6.273816094356294</v>
+        <v>0.6343188236772476</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>GLOS</t>
+          <t>FRAME</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0.8183942053226714</v>
+        <v>0.8178774964065021</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.7385390626868381</v>
+        <v>0.7341250977373035</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.9139814043094668</v>
+        <v>0.8994935530326782</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.7414000921262942</v>
+        <v>0.7333340883925064</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.10810435899591</v>
+        <v>6.273816094356294</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>ILMNN</t>
+          <t>GLOS</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>0.8190716230395246</v>
+        <v>0.8183942053226714</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.7618593926454673</v>
+        <v>0.7385390626868381</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.91072661186667</v>
+        <v>0.9139814043094668</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.7331742443053656</v>
+        <v>0.7414000921262942</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.4237584954605686</v>
+        <v>0.10810435899591</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>imDEF</t>
+          <t>ILMNN</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>0.8266204178002016</v>
+        <v>0.8190716230395246</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.7859040959053544</v>
+        <v>0.7618593926454673</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.9249653709079333</v>
+        <v>0.91072661186667</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.7579644329583753</v>
+        <v>0.7331742443053656</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>14.32176787647523</v>
+        <v>0.4237584954605686</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>LexiBoost</t>
+          <t>imDEF</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>0.681184730874197</v>
+        <v>0.8266204178002016</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.6171572667594937</v>
+        <v>0.7859040959053544</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.8067336935431734</v>
+        <v>0.9249653709079333</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.4744745814286268</v>
+        <v>0.7579644329583753</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.16496927769833</v>
+        <v>14.32176787647523</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>MC-CCR</t>
+          <t>LexiBoost</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>0.8123552383903152</v>
+        <v>0.681184730874197</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.7097531893975606</v>
+        <v>0.6171572667594937</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.910446550433062</v>
+        <v>0.8067336935431734</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.7427916978573005</v>
+        <v>0.4744745814286268</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.1094139523474514</v>
+        <v>0.16496927769833</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>MC-RBO</t>
+          <t>MC-CCR</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>0.8134663720939421</v>
+        <v>0.8123552383903152</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.7093092588929428</v>
+        <v>0.7097531893975606</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.9101732553754301</v>
+        <v>0.910446550433062</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.7402517858714199</v>
+        <v>0.7427916978573005</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>12.26193184011275</v>
+        <v>0.1094139523474514</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>MDO</t>
+          <t>MC-RBO</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>0.8104124530063977</v>
+        <v>0.8134663720939421</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.717435818788466</v>
+        <v>0.7093092588929428</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.913574616086433</v>
+        <v>0.9101732553754301</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.7449601964218471</v>
+        <v>0.7402517858714199</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.1080841237728573</v>
+        <v>12.26193184011275</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>NROMM</t>
+          <t>MDO</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>0.8166219917064932</v>
+        <v>0.8104124530063977</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.7296353914915283</v>
+        <v>0.717435818788466</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.911863543536569</v>
+        <v>0.913574616086433</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.736195333010329</v>
+        <v>0.7449601964218471</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2.553988114342221</v>
+        <v>0.1080841237728573</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>OREM-M</t>
+          <t>NROMM</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>0.8179793103576289</v>
+        <v>0.8166219917064932</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.7427191726891861</v>
+        <v>0.7296353914915283</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.9132797359961885</v>
+        <v>0.911863543536569</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.7319798657498726</v>
+        <v>0.736195333010329</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.2188662339628264</v>
+        <v>2.553988114342221</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>QC-SMOTE</t>
+          <t>OREM-M</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>0.8137564577274202</v>
+        <v>0.8179793103576289</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.7160182717098703</v>
+        <v>0.7427191726891861</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.9139692438858436</v>
+        <v>0.9132797359961885</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.7423863033374953</v>
+        <v>0.7319798657498726</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>12.47311530136955</v>
+        <v>0.2188662339628264</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>SHSampler</t>
+          <t>Ours</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>0.8054039475467032</v>
+        <v>0.6620803083073784</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.8044854051860032</v>
+        <v>0.4611010037937749</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.9153335318365808</v>
+        <v>0.849310647567679</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.7302968933775464</v>
+        <v>0.6192085763080017</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.1058116273278682</v>
+        <v>5.996540689734994</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>SMOM</t>
+          <t>QC-SMOTE</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>0.816838860187057</v>
+        <v>0.8137564577274202</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.7398639224392441</v>
+        <v>0.7160182717098703</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.9144123007898385</v>
+        <v>0.9139692438858436</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.7372226167735224</v>
+        <v>0.7423863033374953</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>26.52670156240987</v>
+        <v>12.47311530136955</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>SOUP</t>
+          <t>SHSampler</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>0.8141914506335174</v>
+        <v>0.8054039475467032</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.7526699109675399</v>
+        <v>0.8044854051860032</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.9134405954423487</v>
+        <v>0.9153335318365808</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.7318567058136517</v>
+        <v>0.7302968933775464</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>9.325543358289012</v>
+        <v>0.1058116273278682</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>SPE</t>
+          <t>SMOM</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>0.7410538586066897</v>
+        <v>0.816838860187057</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.8345396130090291</v>
+        <v>0.7398639224392441</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.902776306062112</v>
+        <v>0.9144123007898385</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.7114640427657584</v>
+        <v>0.7372226167735224</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>11.30964384630186</v>
+        <v>26.52670156240987</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>DualLexiBoost</t>
-        </is>
+          <t>SOUP</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>0.8141914506335174</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>0.7526699109675399</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>0.9134405954423487</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>0.7318567058136517</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>9.325543358289012</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Ours</t>
-        </is>
+          <t>SPE</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>0.7410538586066897</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>0.8345396130090291</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>0.902776306062112</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>0.7114640427657584</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>11.30964384630186</v>
       </c>
     </row>
   </sheetData>
@@ -986,7 +1016,7 @@
         <v>1.75</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="D2" s="6" t="n">
         <v>1</v>
@@ -1001,7 +1031,7 @@
         <v>1</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -1042,7 +1072,7 @@
         <v>6.25</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>6</v>
@@ -1057,7 +1087,7 @@
         <v>7</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -1119,57 +1149,57 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>QC-SMOTE</t>
+          <t>SHSampler</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
         <v>8.25</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>9.6</v>
+        <v>7</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E7" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="F7" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="G7" s="6" t="n">
-        <v>4</v>
-      </c>
       <c r="H7" s="6" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>SHSampler</t>
+          <t>QC-SMOTE</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>8.25</v>
+        <v>8.5</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>7</v>
+        <v>10.2</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
@@ -1179,16 +1209,16 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>8.5</v>
+        <v>8.75</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>12</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>7</v>
@@ -1210,7 +1240,7 @@
         <v>8.75</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>8</v>
@@ -1225,7 +1255,7 @@
         <v>13</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
@@ -1238,7 +1268,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>10.6</v>
+        <v>11</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>13</v>
@@ -1253,7 +1283,7 @@
         <v>9</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
@@ -1266,7 +1296,7 @@
         <v>9.5</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D12" s="6" t="n">
         <v>7</v>
@@ -1281,7 +1311,7 @@
         <v>8</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
@@ -1294,7 +1324,7 @@
         <v>10.5</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>10.6</v>
+        <v>11</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>5</v>
@@ -1309,7 +1339,7 @@
         <v>10</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
@@ -1319,16 +1349,16 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>10.5</v>
+        <v>10.75</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>11</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>13</v>
@@ -1347,13 +1377,13 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>10.75</v>
+        <v>11</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>12.4</v>
+        <v>13</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E15" s="6" t="n">
         <v>1</v>
@@ -1365,7 +1395,7 @@
         <v>16</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16">
@@ -1375,16 +1405,16 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>11.5</v>
+        <v>11.75</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>12</v>
+        <v>12.6</v>
       </c>
       <c r="D16" s="6" t="n">
         <v>10</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>14</v>
@@ -1393,7 +1423,7 @@
         <v>6</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
@@ -1403,13 +1433,13 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>13</v>
+        <v>13.25</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>13</v>
+        <v>13.6</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E17" s="6" t="n">
         <v>2</v>
@@ -1421,7 +1451,7 @@
         <v>17</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
@@ -1431,16 +1461,16 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>15.5</v>
+        <v>15.75</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>14.2</v>
+        <v>14.4</v>
       </c>
       <c r="D18" s="6" t="n">
         <v>15</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>15</v>
@@ -1455,71 +1485,113 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>AdaBoostAD</t>
+          <t>DualLexiBoost</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>18.5</v>
+        <v>17.25</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>15</v>
+        <v>15.8</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G19" s="6" t="n">
         <v>19</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>LexiBoost</t>
+          <t>Ours</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>18.5</v>
+        <v>19.25</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>16</v>
+        <v>17.8</v>
       </c>
       <c r="D20" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="F20" s="6" t="n">
         <v>18</v>
-      </c>
-      <c r="E20" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="F20" s="6" t="n">
-        <v>19</v>
       </c>
       <c r="G20" s="6" t="n">
         <v>18</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>DualLexiBoost</t>
-        </is>
+          <t>LexiBoost</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Ours</t>
-        </is>
+          <t>AdaBoostAD</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1533,7 +1605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1560,67 +1632,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>参与均值与排名的完整模型 19 个; 数据集覆盖不全未参与 2 个</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>排除模型</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>DualLexiBoost: 要求 113 个数据集, 有效结果 111 个, 缺失 2 个 (2 个 keel); 不参与均值与排名, 仅保留模型名</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>排除模型</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Ours: 要求 113 个数据集, 有效结果 112 个, 缺失 1 个 (1 个 keel); 不参与均值与排名, 仅保留模型名</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>失败单元</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>DualLexiBoost × pima: 指标为 NaN/Error, 视为未跑出结果, 不参与聚合</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>失败单元</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Ours × wisconsin: 指标为 NaN/Error, 视为未跑出结果, 不参与聚合</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>失败单元</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>DualLexiBoost × yeast: 指标为 NaN/Error, 视为未跑出结果, 不参与聚合</t>
+          <t>本组 21 个模型均在全部 113 个数据集上跑出结果, 全部参与均值与排名</t>
         </is>
       </c>
     </row>
